--- a/SUPABASE/ANALIZAR/convalidaciones.xlsx
+++ b/SUPABASE/ANALIZAR/convalidaciones.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="375">
   <si>
     <t>ORDEN</t>
   </si>
@@ -33,15 +33,6 @@
     <t>SEMESTRE</t>
   </si>
   <si>
-    <t>SIGLA.1</t>
-  </si>
-  <si>
-    <t>ASIGNATURA.1</t>
-  </si>
-  <si>
-    <t>SEMESTRE.1</t>
-  </si>
-  <si>
     <t>OBSERVACIÓN</t>
   </si>
   <si>
@@ -1144,13 +1135,22 @@
   </si>
   <si>
     <t>PSICOTERAPIA INFANTIL</t>
+  </si>
+  <si>
+    <t>148-2</t>
+  </si>
+  <si>
+    <t>148-1</t>
+  </si>
+  <si>
+    <t>s/n</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1163,8 +1163,16 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1177,8 +1185,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1193,11 +1207,46 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1205,12 +1254,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1513,7 +1581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H131"/>
+  <dimension ref="A1:H132"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -1526,359 +1594,347 @@
     <col min="8" max="8" width="19.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="8"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="H6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G7" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" t="s">
+        <v>7</v>
       </c>
       <c r="H9" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H10" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" t="s">
         <v>38</v>
       </c>
-      <c r="E11" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" t="s">
-        <v>46</v>
-      </c>
       <c r="G11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G12" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E13" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G13" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="H13" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E14" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G14" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -1886,977 +1942,977 @@
         <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E15" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G15" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H15" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F16" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G16" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="H16" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E17" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="F17" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E18" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F18" t="s">
-        <v>74</v>
-      </c>
-      <c r="G18" t="s">
-        <v>38</v>
+        <v>66</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>67</v>
       </c>
       <c r="H18" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D19" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E19" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F19" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G19" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H19" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E20" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F20" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="G20" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H20" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E21" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F21" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H21" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="E22" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F22" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="H22" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E23" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F23" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="G23" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H23" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D24" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E24" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="F24" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="H24" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D25" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E25" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="F25" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="G25" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H25" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D26" t="s">
-        <v>51</v>
+        <v>48</v>
+      </c>
+      <c r="E26" t="s">
+        <v>93</v>
+      </c>
+      <c r="F26" t="s">
+        <v>92</v>
+      </c>
+      <c r="G26" t="s">
+        <v>26</v>
       </c>
       <c r="H26" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D27" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H27" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D28" t="s">
-        <v>65</v>
-      </c>
-      <c r="E28" t="s">
-        <v>103</v>
-      </c>
-      <c r="F28" t="s">
-        <v>102</v>
-      </c>
-      <c r="G28" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H28" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D29" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E29" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="G29" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="H29" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C30" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D30" t="s">
-        <v>65</v>
+        <v>62</v>
+      </c>
+      <c r="E30" t="s">
+        <v>103</v>
+      </c>
+      <c r="F30" t="s">
+        <v>104</v>
+      </c>
+      <c r="G30" t="s">
+        <v>105</v>
       </c>
       <c r="H30" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D31" t="s">
-        <v>65</v>
-      </c>
-      <c r="E31" t="s">
-        <v>113</v>
-      </c>
-      <c r="F31" t="s">
-        <v>114</v>
-      </c>
-      <c r="G31" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="H31" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C32" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E32" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="F32" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G32" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="H32" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D33" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E33" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="F33" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G33" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H33" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B34" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C34" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D34" t="s">
-        <v>108</v>
+        <v>62</v>
       </c>
       <c r="E34" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="F34" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="G34" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="H34" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D35" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E35" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F35" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="G35" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H35" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C36" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D36" t="s">
-        <v>108</v>
+        <v>105</v>
+      </c>
+      <c r="E36" t="s">
+        <v>125</v>
+      </c>
+      <c r="F36" t="s">
+        <v>126</v>
+      </c>
+      <c r="G36" t="s">
+        <v>122</v>
       </c>
       <c r="H36" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C37" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D37" t="s">
-        <v>108</v>
-      </c>
-      <c r="E37" t="s">
-        <v>134</v>
-      </c>
-      <c r="F37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G37" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="H37" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B38" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C38" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="D38" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E38" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F38" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G38" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H38" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C39" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D39" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E39" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="F39" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="G39" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="H39" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C40" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="D40" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E40" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="F40" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G40" t="s">
-        <v>108</v>
+        <v>26</v>
       </c>
       <c r="H40" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B41" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C41" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="D41" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="E41" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="F41" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="G41" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="H41" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B42" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C42" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="D42" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E42" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="F42" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="G42" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="H42" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C43" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D43" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E43" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="F43" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="G43" t="s">
-        <v>155</v>
+        <v>105</v>
       </c>
       <c r="H43" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B44" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C44" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D44" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E44" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="F44" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="G44" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="H44" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B45" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C45" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D45" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E45" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="F45" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="G45" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="H45" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C46" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D46" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E46" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="F46" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="G46" t="s">
-        <v>155</v>
+        <v>62</v>
       </c>
       <c r="H46" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C47" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D47" t="s">
-        <v>155</v>
+        <v>122</v>
       </c>
       <c r="E47" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F47" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G47" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H47" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B48" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C48" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D48" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E48" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F48" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G48" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="H48" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B49" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C49" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D49" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E49" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F49" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="G49" t="s">
-        <v>179</v>
+        <v>105</v>
       </c>
       <c r="H49" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B50" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C50" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D50" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E50" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="F50" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="G50" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="H50" t="s">
-        <v>184</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B51" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C51" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D51" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E51" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="F51" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G51" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="H51" t="s">
-        <v>13</v>
+        <v>181</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B52" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C52" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D52" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E52" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="F52" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="G52" t="s">
-        <v>179</v>
+        <v>105</v>
       </c>
       <c r="H52" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B53" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C53" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D53" t="s">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="E53" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="F53" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="G53" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H53" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -2864,1387 +2920,1608 @@
         <v>1</v>
       </c>
       <c r="B54" t="s">
+        <v>189</v>
+      </c>
+      <c r="C54" t="s">
+        <v>190</v>
+      </c>
+      <c r="D54" t="s">
+        <v>176</v>
+      </c>
+      <c r="E54" t="s">
+        <v>191</v>
+      </c>
+      <c r="F54" t="s">
+        <v>192</v>
+      </c>
+      <c r="G54" t="s">
+        <v>176</v>
+      </c>
+      <c r="H54" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>1</v>
+      </c>
+      <c r="B55" t="s">
+        <v>193</v>
+      </c>
+      <c r="C55" t="s">
+        <v>194</v>
+      </c>
+      <c r="D55" t="s">
+        <v>195</v>
+      </c>
+      <c r="H55" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C56" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D56" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="H54" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="2"/>
-      <c r="B55" s="2" t="s">
+      <c r="F56" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C57" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D55" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E55" s="2" t="s">
+      <c r="D57" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="F57" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="G55" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2" t="s">
+      <c r="G57" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C58" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E56" s="2" t="s">
+      <c r="D58" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F56" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2" t="s">
+      <c r="C59" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="D59" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="D57" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="2"/>
-      <c r="B58" s="2" t="s">
+      <c r="F59" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="G59" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E58" s="2" t="s">
+      <c r="C60" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="D60" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="G58" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2" t="s">
+      <c r="C61" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="D61" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="2"/>
-      <c r="B60" s="2" t="s">
+      <c r="F61" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="G61" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E60" s="2" t="s">
+      <c r="C62" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="D62" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="G60" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2" t="s">
+      <c r="C63" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="D63" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="2"/>
-      <c r="B62" s="2" t="s">
+      <c r="C64" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="D64" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2" t="s">
+      <c r="C65" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="D65" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="D63" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2" t="s">
+      <c r="C66" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B66" t="s">
-        <v>227</v>
-      </c>
-      <c r="C66" t="s">
-        <v>228</v>
-      </c>
-      <c r="D66" t="s">
-        <v>179</v>
-      </c>
-      <c r="E66" t="s">
-        <v>229</v>
-      </c>
-      <c r="F66" t="s">
-        <v>230</v>
-      </c>
-      <c r="G66" t="s">
-        <v>179</v>
-      </c>
-      <c r="H66" t="s">
-        <v>13</v>
+      <c r="D66" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="C67" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="D67" t="s">
-        <v>179</v>
+        <v>176</v>
+      </c>
+      <c r="E67" t="s">
+        <v>226</v>
+      </c>
+      <c r="F67" t="s">
+        <v>227</v>
+      </c>
+      <c r="G67" t="s">
+        <v>176</v>
       </c>
       <c r="H67" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C68" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D68" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H68" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C69" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D69" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H69" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C70" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D70" t="s">
-        <v>179</v>
-      </c>
-      <c r="E70" t="s">
-        <v>239</v>
-      </c>
-      <c r="F70" t="s">
-        <v>240</v>
-      </c>
-      <c r="G70" t="s">
-        <v>125</v>
+        <v>176</v>
       </c>
       <c r="H70" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C71" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="D71" t="s">
-        <v>179</v>
+        <v>176</v>
+      </c>
+      <c r="E71" t="s">
+        <v>236</v>
+      </c>
+      <c r="F71" t="s">
+        <v>237</v>
+      </c>
+      <c r="G71" t="s">
+        <v>122</v>
       </c>
       <c r="H71" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C72" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D72" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="H72" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C73" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D73" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H73" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C74" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D74" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H74" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C75" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D75" t="s">
-        <v>179</v>
-      </c>
-      <c r="E75" t="s">
-        <v>251</v>
-      </c>
-      <c r="F75" t="s">
-        <v>252</v>
-      </c>
-      <c r="G75" t="s">
-        <v>125</v>
+        <v>195</v>
       </c>
       <c r="H75" t="s">
-        <v>184</v>
+        <v>36</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C76" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D76" t="s">
-        <v>179</v>
+        <v>176</v>
+      </c>
+      <c r="E76" t="s">
+        <v>248</v>
+      </c>
+      <c r="F76" t="s">
+        <v>249</v>
+      </c>
+      <c r="G76" t="s">
+        <v>122</v>
       </c>
       <c r="H76" t="s">
-        <v>39</v>
+        <v>181</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C77" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="D77" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H77" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C78" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D78" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="H78" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C79" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D79" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H79" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C80" t="s">
+        <v>257</v>
+      </c>
+      <c r="D80" t="s">
+        <v>195</v>
+      </c>
+      <c r="H80" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
+        <v>258</v>
+      </c>
+      <c r="C81" t="s">
+        <v>259</v>
+      </c>
+      <c r="D81" t="s">
+        <v>195</v>
+      </c>
+      <c r="H81" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>260</v>
+      </c>
+      <c r="C82" t="s">
+        <v>247</v>
+      </c>
+      <c r="D82" t="s">
+        <v>176</v>
+      </c>
+      <c r="E82" t="s">
         <v>261</v>
       </c>
-      <c r="C80" t="s">
+      <c r="F82" t="s">
         <v>262</v>
       </c>
-      <c r="D80" t="s">
-        <v>198</v>
-      </c>
-      <c r="H80" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B81" t="s">
+      <c r="G82" t="s">
+        <v>152</v>
+      </c>
+      <c r="H82" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B83" t="s">
         <v>263</v>
       </c>
-      <c r="C81" t="s">
-        <v>250</v>
-      </c>
-      <c r="D81" t="s">
-        <v>179</v>
-      </c>
-      <c r="E81" t="s">
+      <c r="C83" t="s">
+        <v>251</v>
+      </c>
+      <c r="D83" t="s">
+        <v>176</v>
+      </c>
+      <c r="H83" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
         <v>264</v>
       </c>
-      <c r="F81" t="s">
+      <c r="C84" t="s">
         <v>265</v>
       </c>
-      <c r="G81" t="s">
-        <v>155</v>
-      </c>
-      <c r="H81" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B82" t="s">
+      <c r="D84" t="s">
+        <v>176</v>
+      </c>
+      <c r="H84" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
         <v>266</v>
       </c>
-      <c r="C82" t="s">
-        <v>254</v>
-      </c>
-      <c r="D82" t="s">
-        <v>179</v>
-      </c>
-      <c r="H82" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B83" t="s">
+      <c r="C85" t="s">
+        <v>255</v>
+      </c>
+      <c r="D85" t="s">
+        <v>195</v>
+      </c>
+      <c r="E85" t="s">
         <v>267</v>
       </c>
-      <c r="C83" t="s">
+      <c r="F85" t="s">
         <v>268</v>
       </c>
-      <c r="D83" t="s">
-        <v>179</v>
-      </c>
-      <c r="H83" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B84" t="s">
+      <c r="G85" t="s">
+        <v>176</v>
+      </c>
+      <c r="H85" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
         <v>269</v>
       </c>
-      <c r="C84" t="s">
-        <v>258</v>
-      </c>
-      <c r="D84" t="s">
-        <v>198</v>
-      </c>
-      <c r="E84" t="s">
+      <c r="C86" t="s">
+        <v>257</v>
+      </c>
+      <c r="D86" t="s">
+        <v>195</v>
+      </c>
+      <c r="H86" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="87" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B87" t="s">
         <v>270</v>
       </c>
-      <c r="F84" t="s">
+      <c r="C87" t="s">
+        <v>259</v>
+      </c>
+      <c r="D87" t="s">
+        <v>195</v>
+      </c>
+      <c r="H87" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
         <v>271</v>
       </c>
-      <c r="G84" t="s">
-        <v>179</v>
-      </c>
-      <c r="H84" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B85" t="s">
+      <c r="C88" t="s">
+        <v>247</v>
+      </c>
+      <c r="D88" t="s">
+        <v>176</v>
+      </c>
+      <c r="E88" t="s">
         <v>272</v>
       </c>
-      <c r="C85" t="s">
-        <v>260</v>
-      </c>
-      <c r="D85" t="s">
-        <v>198</v>
-      </c>
-      <c r="H85" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B86" t="s">
+      <c r="F88" t="s">
         <v>273</v>
       </c>
-      <c r="C86" t="s">
-        <v>262</v>
-      </c>
-      <c r="D86" t="s">
-        <v>198</v>
-      </c>
-      <c r="H86" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B87" t="s">
+      <c r="G88" t="s">
+        <v>122</v>
+      </c>
+      <c r="H88" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B89" t="s">
         <v>274</v>
       </c>
-      <c r="C87" t="s">
-        <v>250</v>
-      </c>
-      <c r="D87" t="s">
-        <v>179</v>
-      </c>
-      <c r="E87" t="s">
+      <c r="C89" t="s">
+        <v>251</v>
+      </c>
+      <c r="D89" t="s">
+        <v>176</v>
+      </c>
+      <c r="H89" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B90" t="s">
         <v>275</v>
       </c>
-      <c r="F87" t="s">
+      <c r="C90" t="s">
+        <v>265</v>
+      </c>
+      <c r="D90" t="s">
+        <v>176</v>
+      </c>
+      <c r="H90" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B91" t="s">
         <v>276</v>
       </c>
-      <c r="G87" t="s">
-        <v>125</v>
-      </c>
-      <c r="H87" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B88" t="s">
+      <c r="C91" t="s">
+        <v>255</v>
+      </c>
+      <c r="D91" t="s">
+        <v>195</v>
+      </c>
+      <c r="H91" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B92" t="s">
         <v>277</v>
       </c>
-      <c r="C88" t="s">
-        <v>254</v>
-      </c>
-      <c r="D88" t="s">
-        <v>179</v>
-      </c>
-      <c r="H88" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B89" t="s">
+      <c r="C92" t="s">
+        <v>257</v>
+      </c>
+      <c r="D92" t="s">
+        <v>195</v>
+      </c>
+      <c r="H92" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="93" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B93" t="s">
         <v>278</v>
       </c>
-      <c r="C89" t="s">
-        <v>268</v>
-      </c>
-      <c r="D89" t="s">
-        <v>179</v>
-      </c>
-      <c r="H89" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B90" t="s">
+      <c r="C93" t="s">
+        <v>259</v>
+      </c>
+      <c r="D93" t="s">
+        <v>195</v>
+      </c>
+      <c r="H93" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B94" t="s">
         <v>279</v>
       </c>
-      <c r="C90" t="s">
-        <v>258</v>
-      </c>
-      <c r="D90" t="s">
-        <v>198</v>
-      </c>
-      <c r="H90" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B91" t="s">
+      <c r="C94" t="s">
         <v>280</v>
       </c>
-      <c r="C91" t="s">
-        <v>260</v>
-      </c>
-      <c r="D91" t="s">
-        <v>198</v>
-      </c>
-      <c r="H91" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B92" t="s">
+      <c r="D94" t="s">
+        <v>195</v>
+      </c>
+      <c r="H94" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B95" t="s">
         <v>281</v>
       </c>
-      <c r="C92" t="s">
-        <v>262</v>
-      </c>
-      <c r="D92" t="s">
-        <v>198</v>
-      </c>
-      <c r="H92" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B93" t="s">
+      <c r="C95" t="s">
         <v>282</v>
       </c>
-      <c r="C93" t="s">
+      <c r="D95" t="s">
+        <v>195</v>
+      </c>
+      <c r="H95" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="96" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B96" t="s">
         <v>283</v>
       </c>
-      <c r="D93" t="s">
-        <v>198</v>
-      </c>
-      <c r="H93" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B94" t="s">
+      <c r="C96" t="s">
         <v>284</v>
       </c>
-      <c r="C94" t="s">
+      <c r="D96" t="s">
+        <v>195</v>
+      </c>
+      <c r="H96" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="D94" t="s">
-        <v>198</v>
-      </c>
-      <c r="H94" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B95" t="s">
+      <c r="C97" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C95" t="s">
-        <v>287</v>
-      </c>
-      <c r="D95" t="s">
-        <v>198</v>
-      </c>
-      <c r="H95" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="2"/>
-      <c r="B96" s="2" t="s">
+      <c r="D97" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C98" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="D98" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E98" s="1"/>
+      <c r="F98" s="1"/>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="2"/>
-      <c r="B97" s="2" t="s">
+      <c r="C99" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="D99" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E99" s="1"/>
+      <c r="F99" s="1"/>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="D97" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="2"/>
-      <c r="B98" s="2" t="s">
+      <c r="C100" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="D100" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="D98" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="2"/>
-      <c r="B99" s="2" t="s">
+      <c r="C101" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="D101" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D99" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="2"/>
-      <c r="B100" s="2" t="s">
+      <c r="F101" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="G101" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="D100" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E100" s="2" t="s">
+      <c r="C102" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="F100" s="2" t="s">
+      <c r="D102" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E102" s="1"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="1"/>
+      <c r="H102" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="G100" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="2"/>
-      <c r="B101" s="2" t="s">
+      <c r="C103" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="D103" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E103" s="1"/>
+      <c r="F103" s="1"/>
+      <c r="G103" s="1"/>
+      <c r="H103" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="D101" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-      <c r="H101" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="2"/>
-      <c r="B102" s="2" t="s">
+      <c r="C104" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="D104" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D102" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-      <c r="H102" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="2"/>
-      <c r="B103" s="2" t="s">
+      <c r="F104" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="G104" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="D103" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E103" s="2" t="s">
+      <c r="C105" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="F103" s="2" t="s">
+      <c r="D105" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E105" s="1"/>
+      <c r="F105" s="1"/>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="G103" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="2"/>
-      <c r="B104" s="2" t="s">
+      <c r="C106" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="D106" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E106" s="1"/>
+      <c r="F106" s="1"/>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="D104" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-      <c r="H104" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="2"/>
-      <c r="B105" s="2" t="s">
+      <c r="C107" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="D107" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E107" s="1"/>
+      <c r="F107" s="1"/>
+      <c r="G107" s="1"/>
+      <c r="H107" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="D105" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-      <c r="H105" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="2"/>
-      <c r="B106" s="2" t="s">
+      <c r="C108" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="D108" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E108" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D106" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
-      <c r="H106" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="2"/>
-      <c r="B107" s="2" t="s">
+      <c r="F108" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="G108" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D107" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E107" s="2" t="s">
+      <c r="C109" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="F107" s="2" t="s">
+      <c r="D109" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E109" s="1"/>
+      <c r="F109" s="1"/>
+      <c r="G109" s="1"/>
+      <c r="H109" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="G107" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="2"/>
-      <c r="B108" s="2" t="s">
+      <c r="C110" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="D110" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E110" s="1"/>
+      <c r="F110" s="1"/>
+      <c r="G110" s="1"/>
+      <c r="H110" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="D108" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E108" s="2"/>
-      <c r="F108" s="2"/>
-      <c r="G108" s="2"/>
-      <c r="H108" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="2"/>
-      <c r="B109" s="2" t="s">
+      <c r="C111" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="D111" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E111" s="1"/>
+      <c r="F111" s="1"/>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="D109" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E109" s="2"/>
-      <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
-      <c r="H109" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="2"/>
-      <c r="B110" s="2" t="s">
+      <c r="C112" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="D112" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E112" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="D110" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E110" s="2"/>
-      <c r="F110" s="2"/>
-      <c r="G110" s="2"/>
-      <c r="H110" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="2"/>
-      <c r="B111" s="2" t="s">
+      <c r="F112" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="G112" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="D111" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E111" s="2" t="s">
+      <c r="C113" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="F111" s="2" t="s">
+      <c r="D113" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E113" s="1"/>
+      <c r="F113" s="1"/>
+      <c r="G113" s="1"/>
+      <c r="H113" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="G111" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="2"/>
-      <c r="B112" s="2" t="s">
+      <c r="C114" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="C112" s="2" t="s">
+      <c r="D114" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E114" s="1"/>
+      <c r="F114" s="1"/>
+      <c r="G114" s="1"/>
+      <c r="H114" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="D112" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E112" s="2"/>
-      <c r="F112" s="2"/>
-      <c r="G112" s="2"/>
-      <c r="H112" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" s="2"/>
-      <c r="B113" s="2" t="s">
+      <c r="C115" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="D115" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E115" s="1"/>
+      <c r="F115" s="1"/>
+      <c r="G115" s="1"/>
+      <c r="H115" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="D113" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E113" s="2"/>
-      <c r="F113" s="2"/>
-      <c r="G113" s="2"/>
-      <c r="H113" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" s="2"/>
-      <c r="B114" s="2" t="s">
+      <c r="C116" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="D116" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E116" s="1"/>
+      <c r="F116" s="1"/>
+      <c r="G116" s="1"/>
+      <c r="H116" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="D114" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E114" s="2"/>
-      <c r="F114" s="2"/>
-      <c r="G114" s="2"/>
-      <c r="H114" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="2"/>
-      <c r="B115" s="2" t="s">
+      <c r="C117" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="D117" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E117" s="1"/>
+      <c r="F117" s="1"/>
+      <c r="G117" s="1"/>
+      <c r="H117" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="D115" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E115" s="2"/>
-      <c r="F115" s="2"/>
-      <c r="G115" s="2"/>
-      <c r="H115" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="2"/>
-      <c r="B116" s="2" t="s">
+      <c r="C118" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C116" s="2" t="s">
+      <c r="D118" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E118" s="1"/>
+      <c r="F118" s="1"/>
+      <c r="G118" s="1"/>
+      <c r="H118" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="D116" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E116" s="2"/>
-      <c r="F116" s="2"/>
-      <c r="G116" s="2"/>
-      <c r="H116" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" s="2"/>
-      <c r="B117" s="2" t="s">
+      <c r="C119" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="D119" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="D117" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" s="2"/>
-      <c r="G117" s="2"/>
-      <c r="H117" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" s="2"/>
-      <c r="B118" s="2" t="s">
+      <c r="F119" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="G119" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C120" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="D118" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E118" s="2" t="s">
+      <c r="D120" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E120" s="1"/>
+      <c r="F120" s="1"/>
+      <c r="G120" s="1"/>
+      <c r="H120" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="F118" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="G118" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" s="2"/>
-      <c r="B119" s="2" t="s">
+      <c r="C121" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C119" s="2" t="s">
+      <c r="D121" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E121" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="D119" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" s="2"/>
-      <c r="G119" s="2"/>
-      <c r="H119" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="2"/>
-      <c r="B120" s="2" t="s">
+      <c r="F121" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="G121" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C120" s="2" t="s">
+      <c r="C122" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="D120" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E120" s="2" t="s">
+      <c r="D122" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E122" s="1"/>
+      <c r="F122" s="1"/>
+      <c r="G122" s="1"/>
+      <c r="H122" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="F120" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="G120" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H120" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" s="2"/>
-      <c r="B121" s="2" t="s">
+      <c r="C123" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="C121" s="2" t="s">
+      <c r="D123" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E123" s="1"/>
+      <c r="F123" s="1"/>
+      <c r="G123" s="1"/>
+      <c r="H123" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="D121" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E121" s="2"/>
-      <c r="F121" s="2"/>
-      <c r="G121" s="2"/>
-      <c r="H121" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="2"/>
-      <c r="B122" s="2" t="s">
+      <c r="C124" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="D124" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E124" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="D122" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" s="2"/>
-      <c r="G122" s="2"/>
-      <c r="H122" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="2"/>
-      <c r="B123" s="2" t="s">
+      <c r="F124" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="C123" s="2" t="s">
+      <c r="G124" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="D123" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E123" s="2" t="s">
+      <c r="C125" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="F123" s="2" t="s">
+      <c r="D125" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E125" s="1"/>
+      <c r="F125" s="1"/>
+      <c r="G125" s="1"/>
+      <c r="H125" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="G123" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" s="2"/>
-      <c r="B124" s="2" t="s">
+      <c r="C126" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="D126" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E126" s="1"/>
+      <c r="F126" s="1"/>
+      <c r="G126" s="1"/>
+      <c r="H126" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E127" t="s">
         <v>358</v>
       </c>
-      <c r="D124" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E124" s="2"/>
-      <c r="F124" s="2"/>
-      <c r="G124" s="2"/>
-      <c r="H124" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="2"/>
-      <c r="B125" s="2" t="s">
+      <c r="F127" t="s">
         <v>359</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="G127" t="s">
+        <v>176</v>
+      </c>
+      <c r="H127" t="s">
         <v>360</v>
       </c>
-      <c r="D125" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E125" s="2"/>
-      <c r="F125" s="2"/>
-      <c r="G125" s="2"/>
-      <c r="H125" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E126" t="s">
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E128" t="s">
         <v>361</v>
       </c>
-      <c r="F126" t="s">
+      <c r="F128" t="s">
         <v>362</v>
       </c>
-      <c r="G126" t="s">
-        <v>179</v>
-      </c>
-      <c r="H126" t="s">
+      <c r="G128" t="s">
+        <v>62</v>
+      </c>
+      <c r="H128" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E129" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E127" t="s">
+      <c r="F129" t="s">
         <v>364</v>
       </c>
-      <c r="F127" t="s">
+      <c r="G129" t="s">
+        <v>195</v>
+      </c>
+      <c r="H129" t="s">
         <v>365</v>
       </c>
-      <c r="G127" t="s">
-        <v>65</v>
-      </c>
-      <c r="H127" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E128" t="s">
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E130" t="s">
         <v>366</v>
       </c>
-      <c r="F128" t="s">
+      <c r="F130" t="s">
         <v>367</v>
       </c>
-      <c r="G128" t="s">
-        <v>198</v>
-      </c>
-      <c r="H128" t="s">
+      <c r="G130" t="s">
+        <v>195</v>
+      </c>
+      <c r="H130" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E131" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="129" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E129" t="s">
+      <c r="F131" t="s">
         <v>369</v>
       </c>
-      <c r="F129" t="s">
+      <c r="G131" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H131" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E132" t="s">
         <v>370</v>
       </c>
-      <c r="G129" t="s">
-        <v>198</v>
-      </c>
-      <c r="H129" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="130" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E130" t="s">
+      <c r="F132" t="s">
         <v>371</v>
       </c>
-      <c r="F130" t="s">
-        <v>372</v>
-      </c>
-      <c r="G130" t="s">
-        <v>70</v>
-      </c>
-      <c r="H130" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="131" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E131" t="s">
-        <v>373</v>
-      </c>
-      <c r="F131" t="s">
-        <v>374</v>
-      </c>
-      <c r="G131" t="s">
-        <v>70</v>
-      </c>
-      <c r="H131" t="s">
-        <v>368</v>
+      <c r="G132" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H132" t="s">
+        <v>365</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:H1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/SUPABASE/ANALIZAR/convalidaciones.xlsx
+++ b/SUPABASE/ANALIZAR/convalidaciones.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chuturubi\Documents\REPOSITORIO\HOJA_DE_RUTA\SUPABASE\ANALIZAR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wild-sis\Documents\MI REPOSITORIO\HOJA_DE_RUTA\SUPABASE\ANALIZAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{881BA270-991F-45E1-AF6A-59395F93D282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="-28920" yWindow="-2355" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="369">
   <si>
     <t>ORDEN</t>
   </si>
@@ -834,28 +835,10 @@
     <t>PSI605</t>
   </si>
   <si>
-    <t>PSI700</t>
-  </si>
-  <si>
     <t>PSI 711</t>
   </si>
   <si>
     <t>INTERVENCIÓN CLÍNICA PSICOANALÍTICA</t>
-  </si>
-  <si>
-    <t>PSI701</t>
-  </si>
-  <si>
-    <t>PSI702</t>
-  </si>
-  <si>
-    <t>PSI703</t>
-  </si>
-  <si>
-    <t>PSI704</t>
-  </si>
-  <si>
-    <t>PSI705</t>
   </si>
   <si>
     <t>INV503</t>
@@ -1149,7 +1132,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1260,6 +1243,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1278,7 +1262,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1580,8 +1563,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H132"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -1595,18 +1578,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="8"/>
+      <c r="A1" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="9"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -2034,7 +2017,7 @@
       <c r="F18" t="s">
         <v>66</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="3" t="s">
         <v>67</v>
       </c>
       <c r="H18" t="s">
@@ -2968,7 +2951,7 @@
       <c r="C56" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="D56" s="9" t="s">
+      <c r="D56" s="3" t="s">
         <v>67</v>
       </c>
       <c r="E56" s="1" t="s">
@@ -2977,7 +2960,7 @@
       <c r="F56" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="G56" s="9" t="s">
+      <c r="G56" s="3" t="s">
         <v>67</v>
       </c>
       <c r="H56" s="1" t="s">
@@ -2994,7 +2977,7 @@
       <c r="C57" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D57" s="9" t="s">
+      <c r="D57" s="3" t="s">
         <v>67</v>
       </c>
       <c r="E57" s="1" t="s">
@@ -3003,14 +2986,14 @@
       <c r="F57" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="G57" s="9" t="s">
+      <c r="G57" s="3" t="s">
         <v>67</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>67</v>
       </c>
@@ -3020,7 +3003,7 @@
       <c r="C58" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="D58" s="9" t="s">
+      <c r="D58" s="3" t="s">
         <v>67</v>
       </c>
       <c r="E58" s="1" t="s">
@@ -3029,7 +3012,7 @@
       <c r="F58" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="G58" s="9" t="s">
+      <c r="G58" s="3" t="s">
         <v>67</v>
       </c>
       <c r="H58" s="1" t="s">
@@ -3046,7 +3029,7 @@
       <c r="C59" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D59" s="9" t="s">
+      <c r="D59" s="3" t="s">
         <v>67</v>
       </c>
       <c r="E59" s="1" t="s">
@@ -3055,7 +3038,7 @@
       <c r="F59" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="G59" s="9" t="s">
+      <c r="G59" s="3" t="s">
         <v>67</v>
       </c>
       <c r="H59" s="1" t="s">
@@ -3072,17 +3055,17 @@
       <c r="C60" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D60" s="9" t="s">
+      <c r="D60" s="3" t="s">
         <v>67</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>36</v>
@@ -3098,7 +3081,7 @@
       <c r="C61" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D61" s="9" t="s">
+      <c r="D61" s="3" t="s">
         <v>67</v>
       </c>
       <c r="E61" s="1" t="s">
@@ -3107,7 +3090,7 @@
       <c r="F61" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="G61" s="9" t="s">
+      <c r="G61" s="3" t="s">
         <v>67</v>
       </c>
       <c r="H61" s="1" t="s">
@@ -3124,17 +3107,17 @@
       <c r="C62" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="D62" s="9" t="s">
+      <c r="D62" s="3" t="s">
         <v>67</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>36</v>
@@ -3150,17 +3133,17 @@
       <c r="C63" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D63" s="9" t="s">
+      <c r="D63" s="3" t="s">
         <v>67</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>36</v>
@@ -3176,17 +3159,17 @@
       <c r="C64" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="D64" s="9" t="s">
+      <c r="D64" s="3" t="s">
         <v>67</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>36</v>
@@ -3202,17 +3185,17 @@
       <c r="C65" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D65" s="9" t="s">
+      <c r="D65" s="3" t="s">
         <v>67</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>36</v>
@@ -3228,17 +3211,17 @@
       <c r="C66" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D66" s="9" t="s">
+      <c r="D66" s="3" t="s">
         <v>67</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>36</v>
@@ -3467,7 +3450,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
         <v>258</v>
       </c>
@@ -3481,7 +3464,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>260</v>
       </c>
@@ -3504,7 +3487,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
         <v>263</v>
       </c>
@@ -3518,7 +3501,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
         <v>264</v>
       </c>
@@ -3532,7 +3515,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
         <v>266</v>
       </c>
@@ -3555,7 +3538,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
         <v>269</v>
       </c>
@@ -3569,7 +3552,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
         <v>270</v>
       </c>
@@ -3583,21 +3566,21 @@
         <v>36</v>
       </c>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B88" t="s">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B88" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="E88" t="s">
         <v>271</v>
       </c>
-      <c r="C88" t="s">
-        <v>247</v>
-      </c>
-      <c r="D88" t="s">
-        <v>176</v>
-      </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
         <v>272</v>
-      </c>
-      <c r="F88" t="s">
-        <v>273</v>
       </c>
       <c r="G88" t="s">
         <v>122</v>
@@ -3606,40 +3589,40 @@
         <v>79</v>
       </c>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
+        <v>273</v>
+      </c>
+      <c r="C89" t="s">
         <v>274</v>
       </c>
-      <c r="C89" t="s">
-        <v>251</v>
-      </c>
       <c r="D89" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="H89" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
         <v>275</v>
       </c>
       <c r="C90" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="D90" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="H90" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C91" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="D91" t="s">
         <v>195</v>
@@ -3648,88 +3631,124 @@
         <v>36</v>
       </c>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B92" t="s">
-        <v>277</v>
-      </c>
-      <c r="C92" t="s">
-        <v>257</v>
-      </c>
-      <c r="D92" t="s">
-        <v>195</v>
-      </c>
-      <c r="H92" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B93" t="s">
-        <v>278</v>
-      </c>
-      <c r="C93" t="s">
-        <v>259</v>
-      </c>
-      <c r="D93" t="s">
-        <v>195</v>
-      </c>
-      <c r="H93" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B94" t="s">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C92" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D94" t="s">
-        <v>195</v>
-      </c>
-      <c r="H94" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B95" t="s">
-        <v>281</v>
-      </c>
-      <c r="C95" t="s">
+      <c r="D92" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="D95" t="s">
-        <v>195</v>
-      </c>
-      <c r="H95" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B96" t="s">
+      <c r="C93" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C96" t="s">
+      <c r="D93" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="D96" t="s">
-        <v>195</v>
-      </c>
-      <c r="H96" t="s">
-        <v>36</v>
+      <c r="C94" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E94" s="1"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E95" s="1"/>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
@@ -3740,16 +3759,16 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
@@ -3760,36 +3779,42 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E99" s="1"/>
-      <c r="F99" s="1"/>
-      <c r="G99" s="1"/>
+        <v>281</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>176</v>
+      </c>
       <c r="H99" s="1" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
@@ -3800,42 +3825,36 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="G101" s="9" t="s">
-        <v>67</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
       <c r="H101" s="1" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
@@ -3846,62 +3865,62 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E103" s="1"/>
-      <c r="F103" s="1"/>
-      <c r="G103" s="1"/>
+        <v>281</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="H103" s="1" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>176</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="E104" s="1"/>
+      <c r="F104" s="1"/>
+      <c r="G104" s="1"/>
       <c r="H104" s="1" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
@@ -3912,16 +3931,16 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
@@ -3932,62 +3951,62 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E107" s="1"/>
-      <c r="F107" s="1"/>
-      <c r="G107" s="1"/>
+        <v>281</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="H107" s="1" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>48</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="E108" s="1"/>
+      <c r="F108" s="1"/>
+      <c r="G108" s="1"/>
       <c r="H108" s="1" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E109" s="1"/>
       <c r="F109" s="1"/>
@@ -3998,16 +4017,16 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E110" s="1"/>
       <c r="F110" s="1"/>
@@ -4018,16 +4037,16 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
@@ -4038,42 +4057,36 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>48</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="E112" s="1"/>
+      <c r="F112" s="1"/>
+      <c r="G112" s="1"/>
       <c r="H112" s="1" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
@@ -4084,36 +4097,42 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E114" s="1"/>
-      <c r="F114" s="1"/>
-      <c r="G114" s="1"/>
+        <v>281</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>67</v>
+      </c>
       <c r="H114" s="1" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E115" s="1"/>
       <c r="F115" s="1"/>
@@ -4124,36 +4143,42 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E116" s="1"/>
-      <c r="F116" s="1"/>
-      <c r="G116" s="1"/>
+        <v>281</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>67</v>
+      </c>
       <c r="H116" s="1" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
@@ -4164,16 +4189,16 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
@@ -4184,42 +4209,42 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="G119" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="G119" s="3" t="s">
         <v>67</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>10</v>
+        <v>79</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="E120" s="1"/>
       <c r="F120" s="1"/>
@@ -4230,290 +4255,178 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="G121" s="9" t="s">
-        <v>67</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="E121" s="1"/>
+      <c r="F121" s="1"/>
+      <c r="G121" s="1"/>
       <c r="H121" s="1" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>287</v>
+        <v>368</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E122" s="1"/>
-      <c r="F122" s="1"/>
-      <c r="G122" s="1"/>
-      <c r="H122" s="1" t="s">
-        <v>36</v>
+        <v>368</v>
+      </c>
+      <c r="E122" t="s">
+        <v>352</v>
+      </c>
+      <c r="F122" t="s">
+        <v>353</v>
+      </c>
+      <c r="G122" t="s">
+        <v>176</v>
+      </c>
+      <c r="H122" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>287</v>
+        <v>368</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E123" s="1"/>
-      <c r="F123" s="1"/>
-      <c r="G123" s="1"/>
-      <c r="H123" s="1" t="s">
-        <v>36</v>
+        <v>368</v>
+      </c>
+      <c r="E123" t="s">
+        <v>355</v>
+      </c>
+      <c r="F123" t="s">
+        <v>356</v>
+      </c>
+      <c r="G123" t="s">
+        <v>62</v>
+      </c>
+      <c r="H123" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>287</v>
+        <v>368</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="G124" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="H124" s="1" t="s">
-        <v>79</v>
+        <v>368</v>
+      </c>
+      <c r="E124" t="s">
+        <v>357</v>
+      </c>
+      <c r="F124" t="s">
+        <v>358</v>
+      </c>
+      <c r="G124" t="s">
+        <v>195</v>
+      </c>
+      <c r="H124" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>287</v>
+        <v>368</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E125" s="1"/>
-      <c r="F125" s="1"/>
-      <c r="G125" s="1"/>
-      <c r="H125" s="1" t="s">
-        <v>36</v>
+        <v>368</v>
+      </c>
+      <c r="E125" t="s">
+        <v>360</v>
+      </c>
+      <c r="F125" t="s">
+        <v>361</v>
+      </c>
+      <c r="G125" t="s">
+        <v>195</v>
+      </c>
+      <c r="H125" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>287</v>
+        <v>368</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="E126" s="1"/>
-      <c r="F126" s="1"/>
-      <c r="G126" s="1"/>
-      <c r="H126" s="1" t="s">
-        <v>36</v>
+        <v>368</v>
+      </c>
+      <c r="E126" t="s">
+        <v>362</v>
+      </c>
+      <c r="F126" t="s">
+        <v>363</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H126" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="E127" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="F127" t="s">
+        <v>365</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H127" t="s">
         <v>359</v>
-      </c>
-      <c r="G127" t="s">
-        <v>176</v>
-      </c>
-      <c r="H127" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="E128" t="s">
-        <v>361</v>
-      </c>
-      <c r="F128" t="s">
-        <v>362</v>
-      </c>
-      <c r="G128" t="s">
-        <v>62</v>
-      </c>
-      <c r="H128" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A129" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="E129" t="s">
-        <v>363</v>
-      </c>
-      <c r="F129" t="s">
-        <v>364</v>
-      </c>
-      <c r="G129" t="s">
-        <v>195</v>
-      </c>
-      <c r="H129" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A130" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="E130" t="s">
-        <v>366</v>
-      </c>
-      <c r="F130" t="s">
-        <v>367</v>
-      </c>
-      <c r="G130" t="s">
-        <v>195</v>
-      </c>
-      <c r="H130" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="E131" t="s">
-        <v>368</v>
-      </c>
-      <c r="F131" t="s">
-        <v>369</v>
-      </c>
-      <c r="G131" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="H131" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A132" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="E132" t="s">
-        <v>370</v>
-      </c>
-      <c r="F132" t="s">
-        <v>371</v>
-      </c>
-      <c r="G132" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="H132" t="s">
-        <v>365</v>
       </c>
     </row>
   </sheetData>
